--- a/study_case_model/scenario_variables/price_scenarios111.xlsx
+++ b/study_case_model/scenario_variables/price_scenarios111.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28189.75828697512</v>
+        <v>28.18975828697512</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32270.79793334979</v>
+        <v>32.27079793334979</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30221.76600467628</v>
+        <v>30.22176600467628</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28044.53985083727</v>
+        <v>28.04453985083727</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27631.00654525065</v>
+        <v>27.63100654525065</v>
       </c>
     </row>
   </sheetData>
